--- a/Packages/cn.etetet.excel/Excel/DREntityBaseEntry.xlsx
+++ b/Packages/cn.etetet.excel/Excel/DREntityBaseEntry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lilei/Work/ET9_StateSync/Packages/cn.etetet.excel/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CF94E5-91DB-6C4B-A92F-D46245BF0078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99224C98-7366-0C45-A258-62B0D6C0DA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EntityBaseEntry" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t>编号</t>
   </si>
@@ -126,13 +126,53 @@
   </si>
   <si>
     <t>float</t>
+  </si>
+  <si>
+    <t>模型名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModelName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>red</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>green</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>颜色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Color</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +182,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -170,8 +218,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -654,15 +705,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:P6"/>
+  <dimension ref="C3:R9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:16">
+    <row r="3" spans="3:18">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -702,8 +756,14 @@
       <c r="P3" t="s">
         <v>12</v>
       </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="4" spans="3:16">
+    <row r="4" spans="3:18">
       <c r="C4" t="s">
         <v>13</v>
       </c>
@@ -746,8 +806,14 @@
       <c r="P4" t="s">
         <v>26</v>
       </c>
+      <c r="Q4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="5" spans="3:16">
+    <row r="5" spans="3:18">
       <c r="C5" t="s">
         <v>27</v>
       </c>
@@ -790,8 +856,14 @@
       <c r="P5" t="s">
         <v>30</v>
       </c>
+      <c r="Q5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="6" spans="3:16">
+    <row r="6" spans="3:18">
       <c r="C6">
         <v>1</v>
       </c>
@@ -823,6 +895,135 @@
         <v>1</v>
       </c>
       <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="R6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="3:18">
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>3</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:18">
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>2</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="3:18">
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R9" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Packages/cn.etetet.excel/Excel/DREntityBaseEntry.xlsx
+++ b/Packages/cn.etetet.excel/Excel/DREntityBaseEntry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lilei/Work/ET9_StateSync/Packages/cn.etetet.excel/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99224C98-7366-0C45-A258-62B0D6C0DA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB064567-737C-C041-85B3-200839F0A974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,22 +140,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>red</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>green</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>blue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yellow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>颜色</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -166,6 +150,18 @@
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bard</t>
+  </si>
+  <si>
+    <t>Guard</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>OrcJackalTank</t>
   </si>
 </sst>
 </file>
@@ -713,7 +709,7 @@
     <col min="14" max="14" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:18">
@@ -760,7 +756,7 @@
         <v>31</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="3:18">
@@ -810,7 +806,7 @@
         <v>32</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="3:18">
@@ -860,7 +856,7 @@
         <v>33</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="3:18">
@@ -898,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R6" s="1">
         <v>2</v>
@@ -939,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R7" s="1">
         <v>0</v>
@@ -980,7 +976,7 @@
         <v>1</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R8" s="1">
         <v>3</v>
@@ -1021,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R9" s="1">
         <v>1</v>
